--- a/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R368-StatutRessource.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R368-StatutRessource.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250425120000</t>
+    <t>20250919120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T12:00:00+01:00</t>
+    <t>2025-09-19T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,6 +118,9 @@
     <t>Count</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>Code</t>
   </si>
   <si>
@@ -196,7 +199,7 @@
     <t>Terminé</t>
   </si>
   <si>
-    <t>La ressource est totalement finie. Ce statut s'adresse aux ressources Evaluation de l'individu et Evenements liés à la prise en charge de l'individu dans une structure ESSMS. Resource achevée. Ce statut s'adresse au projet personnalisé ainsi qu'à ses ressources Action et Objectif.</t>
+    <t>La ressource est totalement finie. Resource achevée. Ce statut s'adresse à la ressource Evaluation de l'individu.  Ce statut s'applique également au projet personnalisé ainsi qu'à ses ressources Action et Objectif.</t>
   </si>
   <si>
     <t>VALIDE</t>
@@ -205,7 +208,7 @@
     <t>Validé</t>
   </si>
   <si>
-    <t>Ressource approuvée officiellement par un tiers comme le personnel de santé. Ce statut s'adresse aux ressources Evaluation de l'individu et Evenements liés à la prise en charge de l'individu dans une structure ESSMS.</t>
+    <t>Ressource approuvée officiellement par une personne ou un organisme. Ce statut s'adresse aux ressources Evaluation de l'individu et Evenements liés à la prise en charge de l'individu dans une structure ESSMS.</t>
   </si>
   <si>
     <t>APPROUVE</t>
@@ -214,16 +217,13 @@
     <t>Approuvé</t>
   </si>
   <si>
-    <t>Le professionnel considère la ressource comme correcte. Ce statut s'adresse aux ressources Evaluation de l'individu et Evenements liés à la prise en charge de l'individu dans une structure ESSMS.</t>
+    <t>Le professionnel considère la ressource comme correcte. Ce statut s'adresse à la ressource Evaluation de l'individu.</t>
   </si>
   <si>
     <t>PLANIFIE</t>
   </si>
   <si>
-    <t>Planifié</t>
-  </si>
-  <si>
-    <t>Organiser une activité à l'avance.Ce statut s'adresse aux ressources Evaluation et Evenement</t>
+    <t>Ressource organisée à l’avance pour une activité. Ce statut s'adresse à la ressource Evenements liés à la prise en charge de l'individu dans une structure ESSMS.</t>
   </si>
   <si>
     <t>REALISE</t>
@@ -232,7 +232,7 @@
     <t>Réalisé</t>
   </si>
   <si>
-    <t>Resoource totalement effectuée. Ce statut s'adresse aux ressources Evaluation de l'individu et Evenements liés à la prise en charge de l'individu dans une structure ESSMS.</t>
+    <t>Resoource totalement effectuée. Ce statut s'adresse à la ressource Evenements liés à la prise en charge de l'individu dans une structure ESSMS.</t>
   </si>
   <si>
     <t>ANNULE</t>
@@ -241,7 +241,7 @@
     <t>Annulé</t>
   </si>
   <si>
-    <t>La ressource est supprimée. Ce statut s'adresse aux ressources Evaluation de l'individu et Evenements liés à la prise en charge de l'individu dans une structure ESSMS</t>
+    <t>La ressource n’est plus effective mais le statut est gardé pour historique. Ce statut s'adresse à la ressource Evenements liés à la prise en charge de l'individu dans une structure ESSMS.</t>
   </si>
   <si>
     <t>ACTIF</t>
@@ -583,7 +583,9 @@
       <c r="A22" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="B22" s="2"/>
+      <c r="B22" t="s" s="2">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -597,94 +599,94 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>21</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -699,77 +701,75 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="D5" t="s" s="2">
         <v>69</v>
       </c>
+      <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>70</v>
@@ -783,7 +783,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s" s="2">
         <v>73</v>
@@ -797,7 +797,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s" s="2">
         <v>76</v>
@@ -811,7 +811,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s" s="2">
         <v>79</v>
@@ -825,7 +825,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>82</v>
@@ -839,7 +839,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>85</v>
@@ -853,7 +853,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>88</v>

--- a/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R368-StatutRessource.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R368-StatutRessource.xlsx
@@ -232,7 +232,7 @@
     <t>Réalisé</t>
   </si>
   <si>
-    <t>Resoource totalement effectuée. Ce statut s'adresse à la ressource Evenements liés à la prise en charge de l'individu dans une structure ESSMS.</t>
+    <t>Ressource totalement effectuée. Ce statut s'adresse à la ressource Evenements liés à la prise en charge de l'individu dans une structure ESSMS.</t>
   </si>
   <si>
     <t>ANNULE</t>

--- a/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R368-StatutRessource.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R368-StatutRessource.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>Property</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>PLANIFIE</t>
+  </si>
+  <si>
+    <t>Planifié</t>
   </si>
   <si>
     <t>Ressource organisée à l’avance pour une activité. Ce statut s'adresse à la ressource Evenements liés à la prise en charge de l'individu dans une structure ESSMS.</t>
@@ -765,20 +768,22 @@
       <c r="C5" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>70</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -786,13 +791,13 @@
         <v>58</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -800,13 +805,13 @@
         <v>58</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -814,13 +819,13 @@
         <v>58</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -828,13 +833,13 @@
         <v>58</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
@@ -842,13 +847,13 @@
         <v>58</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
@@ -856,13 +861,13 @@
         <v>58</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
